--- a/00_j23_isotopes.xlsx
+++ b/00_j23_isotopes.xlsx
@@ -3395,6 +3395,18 @@
       <c r="Y31" t="n">
         <v>0.5813116378346285</v>
       </c>
+      <c r="Z31" t="n">
+        <v>3.310708815410503</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.04966063223115755</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2395.313670283826</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>76.46940732346137</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3667,6 +3679,18 @@
       </c>
       <c r="Y34" t="n">
         <v>0.4684812793651074</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.225623367495445</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.04935510242211931</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2445.142766914448</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>67.21312094778968</v>
       </c>
     </row>
     <row r="35">
